--- a/readme_docs/요구사항_정의서_초안_2팀.xlsx
+++ b/readme_docs/요구사항_정의서_초안_2팀.xlsx
@@ -14,21 +14,21 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={135b0011-c6ac-43bc-b4af-b50e130dc8be}</author>
-    <author>tc={6f86256d-26fe-4642-a0f5-5d9edadcbba8}</author>
-    <author>tc={b6836cf9-4dd2-495e-a47f-93a117a79f54}</author>
+    <author>tc={5180701a-d00f-4b8a-bc7a-5009ddfc8e21}</author>
+    <author>tc={7287f752-0f1f-438c-aedb-86e03a9929a9}</author>
+    <author>tc={7e63204b-6ae8-40f0-8a6a-11f0627177d1}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{135b0011-c6ac-43bc-b4af-b50e130dc8be}" ref="A1">
+    <comment authorId="0" xr:uid="{5180701a-d00f-4b8a-bc7a-5009ddfc8e21}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	비회원 토론 참여 못한다고 해야하는데 참관은 가능한 건가? 아니면 참관도 안 되는 건가? -&gt; 여기에 추가 필요함 (비회원 삭제해야한다는 피드백 반영)
+	빨간색은 리뷰 필요함 (같이 결정해야할듯)
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{6f86256d-26fe-4642-a0f5-5d9edadcbba8}" ref="A1">
+    <comment authorId="1" xr:uid="{7287f752-0f1f-438c-aedb-86e03a9929a9}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -37,12 +37,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="2" xr:uid="{b6836cf9-4dd2-495e-a47f-93a117a79f54}" ref="A1">
+    <comment authorId="2" xr:uid="{7e63204b-6ae8-40f0-8a6a-11f0627177d1}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	빨간색은 리뷰 필요함 (같이 결정해야할듯)
+	비회원 토론 참여 못한다고 해야하는데 참관은 가능한 건가? 아니면 참관도 안 되는 건가? -&gt; 여기에 추가 필요함 (비회원 삭제해야한다는 피드백 반영)
 </t>
       </text>
     </comment>
@@ -2808,8 +2808,8 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Kat Park" id="{90a5592c-43ab-42e3-b46b-113532b1d4c8}" providerId="google-sheets"/>
-  <x18tc:person displayName="‍전윤우[졸업생 / 언어인지과학과]" id="{bd482680-759c-4424-8c69-5ac8ce658c5d}" providerId="google-sheets"/>
+  <x18tc:person displayName="Kat Park" id="{75e6e291-455a-4b3f-b2ad-9ed2d9d620ff}" providerId="google-sheets"/>
+  <x18tc:person displayName="‍전윤우[졸업생 / 언어인지과학과]" id="{ac8553ab-7582-4980-9b38-79a5b750a452}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -3009,13 +3009,13 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="A1" dT="2026-05-18T16:23:11.00" personId="{bd482680-759c-4424-8c69-5ac8ce658c5d}" id="{135b0011-c6ac-43bc-b4af-b50e130dc8be}" done="1">
+  <x18tc:threadedComment ref="A1" dT="2026-05-18T16:23:11.00" personId="{ac8553ab-7582-4980-9b38-79a5b750a452}" id="{7e63204b-6ae8-40f0-8a6a-11f0627177d1}" done="1">
     <x18tc:text xml:space="preserve">비회원 토론 참여 못한다고 해야하는데 참관은 가능한 건가? 아니면 참관도 안 되는 건가? -&gt; 여기에 추가 필요함 (비회원 삭제해야한다는 피드백 반영)</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-05-18T15:26:13.00" personId="{90a5592c-43ab-42e3-b46b-113532b1d4c8}" id="{b6836cf9-4dd2-495e-a47f-93a117a79f54}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-05-18T15:26:13.00" personId="{75e6e291-455a-4b3f-b2ad-9ed2d9d620ff}" id="{5180701a-d00f-4b8a-bc7a-5009ddfc8e21}" done="0">
     <x18tc:text xml:space="preserve">빨간색은 리뷰 필요함 (같이 결정해야할듯)</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-05-18T08:12:47.00" personId="{90a5592c-43ab-42e3-b46b-113532b1d4c8}" id="{6f86256d-26fe-4642-a0f5-5d9edadcbba8}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-05-18T08:12:47.00" personId="{75e6e291-455a-4b3f-b2ad-9ed2d9d620ff}" id="{7287f752-0f1f-438c-aedb-86e03a9929a9}" done="0">
     <x18tc:text xml:space="preserve">찾기랑 발급은 다름</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
